--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67729_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67729_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R908c05c5318c4fd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R98dd9c1135ef49a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7446</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7446</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9080</x:v>
+        <x:v>      1.9243</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9080</x:v>
+        <x:v>      1.8326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0022</x:v>
+        <x:v>      1.9243</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9080</x:v>
+        <x:v>      1.8326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9080</x:v>
+        <x:v>      1.8326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1003</x:v>
+        <x:v>      2.0197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2022</x:v>
+        <x:v>      2.1190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2022</x:v>
+        <x:v>      2.1190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2022</x:v>
+        <x:v>      2.1190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2022</x:v>
+        <x:v>      2.1190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3083</x:v>
+        <x:v>      2.2222</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3083</x:v>
+        <x:v>      2.2222</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4184</x:v>
+        <x:v>      2.3296</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67729_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67729_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R98dd9c1135ef49a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3d5021203865418e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7446</x:v>
+        <x:v>      1.9102</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6602</x:v>
+        <x:v>      1.6475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7446</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6602</x:v>
+        <x:v>      1.6475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8326</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8326</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8326</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8326</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0197</x:v>
+        <x:v>      2.0052</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9243</x:v>
+        <x:v>      1.9102</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8326</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9243</x:v>
+        <x:v>      1.9102</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8326</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8326</x:v>
+        <x:v>      1.8191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0197</x:v>
+        <x:v>      2.0052</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1190</x:v>
+        <x:v>      2.1040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1190</x:v>
+        <x:v>      2.1040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1190</x:v>
+        <x:v>      2.1040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1190</x:v>
+        <x:v>      2.1040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2222</x:v>
+        <x:v>      2.2067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2222</x:v>
+        <x:v>      2.2067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3296</x:v>
+        <x:v>      2.3136</x:v>
       </x:c>
     </x:row>
     <x:row>
